--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_28.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4535 +469,5115 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:27.324</t>
+          <t>2026-05-29 09:47:49.283</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779509303086</v>
+        <v>1780022867813</v>
       </c>
       <c r="C2" t="n">
-        <v>88174</v>
+        <v>77318</v>
       </c>
       <c r="D2" t="n">
-        <v>-777.08</v>
+        <v>1216.25</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>684</v>
+        <v>1499</v>
       </c>
       <c r="G2" t="n">
-        <v>132.02</v>
+        <v>375.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L2" t="n">
+        <v>111</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.492</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:27.515</t>
+          <t>2026-05-29 09:47:49.326</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779509303287</v>
+        <v>1780022868013</v>
       </c>
       <c r="C3" t="n">
-        <v>88382</v>
+        <v>77490</v>
       </c>
       <c r="D3" t="n">
-        <v>-530.23</v>
+        <v>1327.43</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>1499</v>
       </c>
       <c r="G3" t="n">
-        <v>132.02</v>
+        <v>375.99</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1312</v>
+      </c>
+      <c r="L3" t="n">
+        <v>103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:27.805</t>
+          <t>2026-05-29 09:47:49.357</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779509303489</v>
+        <v>1780022868213</v>
       </c>
       <c r="C4" t="n">
-        <v>88172</v>
+        <v>77504</v>
       </c>
       <c r="D4" t="n">
-        <v>-713.72</v>
+        <v>1275.06</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>1470</v>
+        <v>1499</v>
       </c>
       <c r="G4" t="n">
-        <v>264.82</v>
+        <v>375.99</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1143</v>
+      </c>
+      <c r="L4" t="n">
+        <v>112</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:28.316</t>
+          <t>2026-05-29 09:47:49.360</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779509303690</v>
+        <v>1780022868432</v>
       </c>
       <c r="C5" t="n">
-        <v>88231</v>
+        <v>77072</v>
       </c>
       <c r="D5" t="n">
-        <v>-619.03</v>
+        <v>779.3099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>1470</v>
+        <v>1499</v>
       </c>
       <c r="G5" t="n">
-        <v>264.82</v>
+        <v>375.99</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K5" t="n">
+        <v>927</v>
+      </c>
+      <c r="L5" t="n">
+        <v>110</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:28.570</t>
+          <t>2026-05-29 09:47:50.897</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779509303891</v>
+        <v>1780022868632</v>
       </c>
       <c r="C6" t="n">
-        <v>88434</v>
+        <v>77170</v>
       </c>
       <c r="D6" t="n">
-        <v>-385.08</v>
+        <v>838.34</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>524</v>
+        <v>1499</v>
       </c>
       <c r="G6" t="n">
-        <v>280.12</v>
+        <v>375.99</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2264</v>
+      </c>
+      <c r="L6" t="n">
+        <v>109</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:28.571</t>
+          <t>2026-05-29 09:47:50.897</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779509304093</v>
+        <v>1780022868832</v>
       </c>
       <c r="C7" t="n">
-        <v>88133</v>
+        <v>78202</v>
       </c>
       <c r="D7" t="n">
-        <v>-666.83</v>
+        <v>1828.43</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>524</v>
+        <v>1499</v>
       </c>
       <c r="G7" t="n">
-        <v>280.12</v>
+        <v>375.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2065</v>
+      </c>
+      <c r="L7" t="n">
+        <v>114</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.497</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:28.611</t>
+          <t>2026-05-29 09:47:50.898</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779509304294</v>
+        <v>1780022869032</v>
       </c>
       <c r="C8" t="n">
-        <v>88423</v>
+        <v>79190</v>
       </c>
       <c r="D8" t="n">
-        <v>-343.49</v>
+        <v>2725.01</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>524</v>
+        <v>1499</v>
       </c>
       <c r="G8" t="n">
-        <v>280.12</v>
+        <v>375.99</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1866</v>
+      </c>
+      <c r="L8" t="n">
+        <v>119</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.446</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:28.839</t>
+          <t>2026-05-29 09:47:50.899</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779509304495</v>
+        <v>1780022869232</v>
       </c>
       <c r="C9" t="n">
-        <v>88999</v>
+        <v>78722</v>
       </c>
       <c r="D9" t="n">
-        <v>249.69</v>
+        <v>2120.75</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G9" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1667</v>
+      </c>
+      <c r="L9" t="n">
+        <v>109</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:28.845</t>
+          <t>2026-05-29 09:47:50.900</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779509304697</v>
+        <v>1780022869432</v>
       </c>
       <c r="C10" t="n">
-        <v>88951</v>
+        <v>78164</v>
       </c>
       <c r="D10" t="n">
-        <v>189.2</v>
+        <v>1456.72</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G10" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1467</v>
+      </c>
+      <c r="L10" t="n">
+        <v>116</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.438</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:29.121</t>
+          <t>2026-05-29 09:47:50.900</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779509304898</v>
+        <v>1780022869632</v>
       </c>
       <c r="C11" t="n">
-        <v>89284</v>
+        <v>77769</v>
       </c>
       <c r="D11" t="n">
-        <v>512.74</v>
+        <v>988.88</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G11" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L11" t="n">
+        <v>110</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:29.368</t>
+          <t>2026-05-29 09:47:50.907</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779509305099</v>
+        <v>1780022869851</v>
       </c>
       <c r="C12" t="n">
-        <v>89495</v>
+        <v>78493</v>
       </c>
       <c r="D12" t="n">
-        <v>698.11</v>
+        <v>1663.44</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G12" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1055</v>
+      </c>
+      <c r="L12" t="n">
+        <v>109</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.446</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:29.649</t>
+          <t>2026-05-29 09:47:51.207</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779509305301</v>
+        <v>1780022870051</v>
       </c>
       <c r="C13" t="n">
-        <v>88949</v>
+        <v>78988</v>
       </c>
       <c r="D13" t="n">
-        <v>117.2</v>
+        <v>2075.27</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G13" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L13" t="n">
+        <v>112</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.218</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:29.651</t>
+          <t>2026-05-29 09:47:51.295</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779509305502</v>
+        <v>1780022870251</v>
       </c>
       <c r="C14" t="n">
-        <v>88087</v>
+        <v>78912</v>
       </c>
       <c r="D14" t="n">
-        <v>-750.66</v>
+        <v>1895.5</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G14" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1043</v>
+      </c>
+      <c r="L14" t="n">
+        <v>111</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.204</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:30.135</t>
+          <t>2026-05-29 09:47:51.468</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779509305703</v>
+        <v>1780022870451</v>
       </c>
       <c r="C15" t="n">
-        <v>88924</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="n">
-        <v>123.87</v>
+        <v>1920.73</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G15" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1016</v>
+      </c>
+      <c r="L15" t="n">
+        <v>105</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.503</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:30.463</t>
+          <t>2026-05-29 09:47:51.799</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779509305905</v>
+        <v>1780022870651</v>
       </c>
       <c r="C16" t="n">
-        <v>88780</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="n">
-        <v>-26.32</v>
+        <v>2327.69</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G16" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1147</v>
+      </c>
+      <c r="L16" t="n">
+        <v>115</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.945</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:30.464</t>
+          <t>2026-05-29 09:47:51.801</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779509306106</v>
+        <v>1780022870851</v>
       </c>
       <c r="C17" t="n">
-        <v>88134</v>
+        <v>79141</v>
       </c>
       <c r="D17" t="n">
-        <v>-671</v>
+        <v>1817.31</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G17" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>949</v>
+      </c>
+      <c r="L17" t="n">
+        <v>114</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.846</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:30.465</t>
+          <t>2026-05-29 09:47:52.214</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779509306308</v>
+        <v>1780022871051</v>
       </c>
       <c r="C18" t="n">
-        <v>88002</v>
+        <v>79165</v>
       </c>
       <c r="D18" t="n">
-        <v>-769.45</v>
+        <v>1750.44</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G18" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L18" t="n">
+        <v>114</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.976</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:30.685</t>
+          <t>2026-05-29 09:47:52.215</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779509306509</v>
+        <v>1780022871270</v>
       </c>
       <c r="C19" t="n">
-        <v>87965</v>
+        <v>78606</v>
       </c>
       <c r="D19" t="n">
-        <v>-767.98</v>
+        <v>1103.92</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G19" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>944</v>
+      </c>
+      <c r="L19" t="n">
+        <v>104</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.978</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:30.700</t>
+          <t>2026-05-29 09:47:52.615</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779509306710</v>
+        <v>1780022871470</v>
       </c>
       <c r="C20" t="n">
-        <v>88104</v>
+        <v>78691</v>
       </c>
       <c r="D20" t="n">
-        <v>-590.58</v>
+        <v>1133.72</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G20" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L20" t="n">
+        <v>116</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.531</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:31.066</t>
+          <t>2026-05-29 09:47:52.617</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779509306912</v>
+        <v>1780022871670</v>
       </c>
       <c r="C21" t="n">
-        <v>87769</v>
+        <v>78371</v>
       </c>
       <c r="D21" t="n">
-        <v>-896.05</v>
+        <v>757.04</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G21" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>946</v>
+      </c>
+      <c r="L21" t="n">
+        <v>107</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.413</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:31.334</t>
+          <t>2026-05-29 09:47:53.359</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779509307113</v>
+        <v>1780022871870</v>
       </c>
       <c r="C22" t="n">
-        <v>87838</v>
+        <v>78144</v>
       </c>
       <c r="D22" t="n">
-        <v>-782.25</v>
+        <v>492.18</v>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G22" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1488</v>
+      </c>
+      <c r="L22" t="n">
+        <v>112</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.971</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:31.887</t>
+          <t>2026-05-29 09:47:53.360</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779509307314</v>
+        <v>1780022872070</v>
       </c>
       <c r="C23" t="n">
-        <v>87962</v>
+        <v>78177</v>
       </c>
       <c r="D23" t="n">
-        <v>-619.14</v>
+        <v>500.58</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>604</v>
+        <v>1499</v>
       </c>
       <c r="G23" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1289</v>
+      </c>
+      <c r="L23" t="n">
+        <v>110</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:32.167</t>
+          <t>2026-05-29 09:47:54.007</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779509307516</v>
+        <v>1780022872270</v>
       </c>
       <c r="C24" t="n">
-        <v>87723</v>
+        <v>78014</v>
       </c>
       <c r="D24" t="n">
-        <v>-827.1799999999999</v>
+        <v>312.55</v>
       </c>
       <c r="E24" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>2960</v>
+        <v>1499</v>
       </c>
       <c r="G24" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L24" t="n">
+        <v>114</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.635</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:32.169</t>
+          <t>2026-05-29 09:47:54.009</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779509307717</v>
+        <v>1780022872470</v>
       </c>
       <c r="C25" t="n">
-        <v>87816</v>
+        <v>77740</v>
       </c>
       <c r="D25" t="n">
-        <v>-692.8200000000001</v>
+        <v>22.92</v>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>2960</v>
+        <v>1499</v>
       </c>
       <c r="G25" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1538</v>
+      </c>
+      <c r="L25" t="n">
+        <v>109</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.081</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:32.171</t>
+          <t>2026-05-29 09:47:54.050</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779509307919</v>
+        <v>1780022872670</v>
       </c>
       <c r="C26" t="n">
-        <v>87998</v>
+        <v>77983</v>
       </c>
       <c r="D26" t="n">
-        <v>-476.18</v>
+        <v>264.77</v>
       </c>
       <c r="E26" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>2960</v>
+        <v>1499</v>
       </c>
       <c r="G26" t="n">
-        <v>282.63</v>
+        <v>375.99</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1379</v>
+      </c>
+      <c r="L26" t="n">
+        <v>107</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:32.440</t>
+          <t>2026-05-29 09:47:54.082</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779509308120</v>
+        <v>1780022872889</v>
       </c>
       <c r="C27" t="n">
-        <v>88158</v>
+        <v>77762</v>
       </c>
       <c r="D27" t="n">
-        <v>-292.37</v>
+        <v>30.53</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>564</v>
+        <v>1499</v>
       </c>
       <c r="G27" t="n">
-        <v>290.94</v>
+        <v>375.99</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L27" t="n">
+        <v>108</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.714</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:32.442</t>
+          <t>2026-05-29 09:47:54.659</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779509308321</v>
+        <v>1780022873089</v>
       </c>
       <c r="C28" t="n">
-        <v>87930</v>
+        <v>77856</v>
       </c>
       <c r="D28" t="n">
-        <v>-505.75</v>
+        <v>123.01</v>
       </c>
       <c r="E28" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>564</v>
+        <v>1499</v>
       </c>
       <c r="G28" t="n">
-        <v>290.94</v>
+        <v>375.99</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1569</v>
+      </c>
+      <c r="L28" t="n">
+        <v>116</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.538</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.022</t>
+          <t>2026-05-29 09:47:54.661</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779509308523</v>
+        <v>1780022873289</v>
       </c>
       <c r="C29" t="n">
-        <v>87990</v>
+        <v>78013</v>
       </c>
       <c r="D29" t="n">
-        <v>-420.47</v>
+        <v>273.86</v>
       </c>
       <c r="E29" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>564</v>
+        <v>1499</v>
       </c>
       <c r="G29" t="n">
-        <v>290.94</v>
+        <v>375.99</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1371</v>
+      </c>
+      <c r="L29" t="n">
+        <v>115</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.372</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.300</t>
+          <t>2026-05-29 09:47:54.663</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779509308724</v>
+        <v>1780022873489</v>
       </c>
       <c r="C30" t="n">
-        <v>88108</v>
+        <v>77795</v>
       </c>
       <c r="D30" t="n">
-        <v>-281.44</v>
+        <v>42.16</v>
       </c>
       <c r="E30" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
-        <v>685</v>
+        <v>5736</v>
       </c>
       <c r="G30" t="n">
-        <v>291.74</v>
+        <v>375.99</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1173</v>
+      </c>
+      <c r="L30" t="n">
+        <v>110</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.301</t>
+          <t>2026-05-29 09:47:54.967</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779509308925</v>
+        <v>1780022873689</v>
       </c>
       <c r="C31" t="n">
-        <v>87840</v>
+        <v>77864</v>
       </c>
       <c r="D31" t="n">
-        <v>-535.37</v>
+        <v>109.06</v>
       </c>
       <c r="E31" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>685</v>
+        <v>5736</v>
       </c>
       <c r="G31" t="n">
-        <v>291.74</v>
+        <v>375.99</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L31" t="n">
+        <v>114</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.148</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.302</t>
+          <t>2026-05-29 09:47:54.969</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779509309127</v>
+        <v>1780022873889</v>
       </c>
       <c r="C32" t="n">
-        <v>87890</v>
+        <v>77997</v>
       </c>
       <c r="D32" t="n">
-        <v>-458.6</v>
+        <v>236.6</v>
       </c>
       <c r="E32" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="F32" t="n">
-        <v>685</v>
+        <v>5736</v>
       </c>
       <c r="G32" t="n">
-        <v>291.74</v>
+        <v>375.99</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L32" t="n">
+        <v>113</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.008</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.583</t>
+          <t>2026-05-29 09:47:55.247</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779509309328</v>
+        <v>1780022874089</v>
       </c>
       <c r="C33" t="n">
-        <v>88211</v>
+        <v>78023</v>
       </c>
       <c r="D33" t="n">
-        <v>-114.67</v>
+        <v>250.77</v>
       </c>
       <c r="E33" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F33" t="n">
-        <v>685</v>
+        <v>660</v>
       </c>
       <c r="G33" t="n">
-        <v>291.74</v>
+        <v>386.3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L33" t="n">
+        <v>108</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.600</t>
+          <t>2026-05-29 09:47:55.250</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779509309529</v>
+        <v>1780022874289</v>
       </c>
       <c r="C34" t="n">
-        <v>90539</v>
+        <v>77574</v>
       </c>
       <c r="D34" t="n">
-        <v>2219.06</v>
+        <v>-210.77</v>
       </c>
       <c r="E34" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F34" t="n">
-        <v>745</v>
+        <v>660</v>
       </c>
       <c r="G34" t="n">
-        <v>279.88</v>
+        <v>386.3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>959</v>
+      </c>
+      <c r="L34" t="n">
+        <v>110</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.961</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:33.913</t>
+          <t>2026-05-29 09:47:55.702</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779509309731</v>
+        <v>1780022874508</v>
       </c>
       <c r="C35" t="n">
-        <v>88639</v>
+        <v>77664</v>
       </c>
       <c r="D35" t="n">
-        <v>208.11</v>
+        <v>-110.23</v>
       </c>
       <c r="E35" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F35" t="n">
-        <v>745</v>
+        <v>660</v>
       </c>
       <c r="G35" t="n">
-        <v>279.88</v>
+        <v>386.3</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1193</v>
+      </c>
+      <c r="L35" t="n">
+        <v>110</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.008</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:34.211</t>
+          <t>2026-05-29 09:47:55.711</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779509309932</v>
+        <v>1780022874708</v>
       </c>
       <c r="C36" t="n">
-        <v>88469</v>
+        <v>77767</v>
       </c>
       <c r="D36" t="n">
-        <v>27.7</v>
+        <v>-1.72</v>
       </c>
       <c r="E36" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F36" t="n">
-        <v>745</v>
+        <v>660</v>
       </c>
       <c r="G36" t="n">
-        <v>279.88</v>
+        <v>386.3</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1002</v>
+      </c>
+      <c r="L36" t="n">
+        <v>119</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.024</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:34.468</t>
+          <t>2026-05-29 09:47:56.068</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779509310134</v>
+        <v>1780022874908</v>
       </c>
       <c r="C37" t="n">
-        <v>88659</v>
+        <v>77452</v>
       </c>
       <c r="D37" t="n">
-        <v>216.32</v>
+        <v>-316.63</v>
       </c>
       <c r="E37" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F37" t="n">
-        <v>745</v>
+        <v>819</v>
       </c>
       <c r="G37" t="n">
-        <v>279.88</v>
+        <v>357.46</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L37" t="n">
+        <v>107</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.111</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:34.471</t>
+          <t>2026-05-29 09:47:56.069</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779509310335</v>
+        <v>1780022875108</v>
       </c>
       <c r="C38" t="n">
-        <v>88439</v>
+        <v>77440</v>
       </c>
       <c r="D38" t="n">
-        <v>-14.5</v>
+        <v>-312.8</v>
       </c>
       <c r="E38" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F38" t="n">
-        <v>745</v>
+        <v>819</v>
       </c>
       <c r="G38" t="n">
-        <v>279.88</v>
+        <v>357.46</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>960</v>
+      </c>
+      <c r="L38" t="n">
+        <v>104</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.086</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:34.474</t>
+          <t>2026-05-29 09:47:56.549</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779509310536</v>
+        <v>1780022875308</v>
       </c>
       <c r="C39" t="n">
-        <v>88796</v>
+        <v>77522</v>
       </c>
       <c r="D39" t="n">
-        <v>343.23</v>
+        <v>-215.16</v>
       </c>
       <c r="E39" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F39" t="n">
-        <v>745</v>
+        <v>819</v>
       </c>
       <c r="G39" t="n">
-        <v>279.88</v>
+        <v>357.46</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L39" t="n">
+        <v>107</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.763</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:34.957</t>
+          <t>2026-05-29 09:47:56.550</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779509310738</v>
+        <v>1780022875508</v>
       </c>
       <c r="C40" t="n">
-        <v>88744</v>
+        <v>77321</v>
       </c>
       <c r="D40" t="n">
-        <v>274.07</v>
+        <v>-405.4</v>
       </c>
       <c r="E40" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F40" t="n">
-        <v>745</v>
+        <v>819</v>
       </c>
       <c r="G40" t="n">
-        <v>279.88</v>
+        <v>357.46</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L40" t="n">
+        <v>101</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.828</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:35.216</t>
+          <t>2026-05-29 09:47:56.984</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779509310939</v>
+        <v>1780022875708</v>
       </c>
       <c r="C41" t="n">
-        <v>88975</v>
+        <v>77307</v>
       </c>
       <c r="D41" t="n">
-        <v>491.36</v>
+        <v>-399.13</v>
       </c>
       <c r="E41" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F41" t="n">
-        <v>745</v>
+        <v>819</v>
       </c>
       <c r="G41" t="n">
-        <v>279.88</v>
+        <v>357.46</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L41" t="n">
+        <v>109</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.701</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:35.675</t>
+          <t>2026-05-29 09:47:56.992</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779509311140</v>
+        <v>1780022875908</v>
       </c>
       <c r="C42" t="n">
-        <v>88495</v>
+        <v>77448</v>
       </c>
       <c r="D42" t="n">
-        <v>-13.21</v>
+        <v>-238.17</v>
       </c>
       <c r="E42" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F42" t="n">
-        <v>745</v>
+        <v>819</v>
       </c>
       <c r="G42" t="n">
-        <v>279.88</v>
+        <v>357.46</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L42" t="n">
+        <v>104</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:35.944</t>
+          <t>2026-05-29 09:47:58.667</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779509311342</v>
+        <v>1780022876127</v>
       </c>
       <c r="C43" t="n">
-        <v>88250</v>
+        <v>77471</v>
       </c>
       <c r="D43" t="n">
-        <v>-257.55</v>
+        <v>-203.27</v>
       </c>
       <c r="E43" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F43" t="n">
-        <v>745</v>
+        <v>1260</v>
       </c>
       <c r="G43" t="n">
-        <v>279.88</v>
+        <v>370.53</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2540</v>
+      </c>
+      <c r="L43" t="n">
+        <v>111</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.757</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:35.945</t>
+          <t>2026-05-29 09:47:58.668</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779509311543</v>
+        <v>1780022876327</v>
       </c>
       <c r="C44" t="n">
-        <v>87963</v>
+        <v>77266</v>
       </c>
       <c r="D44" t="n">
-        <v>-531.67</v>
+        <v>-398.1</v>
       </c>
       <c r="E44" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F44" t="n">
-        <v>745</v>
+        <v>1260</v>
       </c>
       <c r="G44" t="n">
-        <v>279.88</v>
+        <v>370.53</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2341</v>
+      </c>
+      <c r="L44" t="n">
+        <v>112</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.756</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:35.972</t>
+          <t>2026-05-29 09:47:58.670</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779509311744</v>
+        <v>1780022876527</v>
       </c>
       <c r="C45" t="n">
-        <v>88137</v>
+        <v>77347</v>
       </c>
       <c r="D45" t="n">
-        <v>-331.08</v>
+        <v>-297.2</v>
       </c>
       <c r="E45" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F45" t="n">
-        <v>745</v>
+        <v>1260</v>
       </c>
       <c r="G45" t="n">
-        <v>279.88</v>
+        <v>370.53</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2142</v>
+      </c>
+      <c r="L45" t="n">
+        <v>113</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.341</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:36.231</t>
+          <t>2026-05-29 09:47:58.671</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779509311946</v>
+        <v>1780022876727</v>
       </c>
       <c r="C46" t="n">
-        <v>87976</v>
+        <v>77231</v>
       </c>
       <c r="D46" t="n">
-        <v>-475.53</v>
+        <v>-398.34</v>
       </c>
       <c r="E46" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F46" t="n">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="G46" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1943</v>
+      </c>
+      <c r="L46" t="n">
+        <v>105</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.873</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:36.232</t>
+          <t>2026-05-29 09:47:58.673</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779509312147</v>
+        <v>1780022876927</v>
       </c>
       <c r="C47" t="n">
-        <v>87509</v>
+        <v>76829</v>
       </c>
       <c r="D47" t="n">
-        <v>-918.75</v>
+        <v>-780.42</v>
       </c>
       <c r="E47" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F47" t="n">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="G47" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1745</v>
+      </c>
+      <c r="L47" t="n">
+        <v>105</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.331</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:36.232</t>
+          <t>2026-05-29 09:47:58.685</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779509312349</v>
+        <v>1780022877127</v>
       </c>
       <c r="C48" t="n">
-        <v>87311</v>
+        <v>76877</v>
       </c>
       <c r="D48" t="n">
-        <v>-1070.82</v>
+        <v>-693.4</v>
       </c>
       <c r="E48" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F48" t="n">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="G48" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1556</v>
+      </c>
+      <c r="L48" t="n">
+        <v>110</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.212</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:36.791</t>
+          <t>2026-05-29 09:47:59.071</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779509312550</v>
+        <v>1780022877327</v>
       </c>
       <c r="C49" t="n">
-        <v>87319</v>
+        <v>77029</v>
       </c>
       <c r="D49" t="n">
-        <v>-1009.28</v>
+        <v>-506.73</v>
       </c>
       <c r="E49" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F49" t="n">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="G49" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1743</v>
+      </c>
+      <c r="L49" t="n">
+        <v>105</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.924</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:37.109</t>
+          <t>2026-05-29 09:47:59.072</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779509312751</v>
+        <v>1780022877527</v>
       </c>
       <c r="C50" t="n">
-        <v>86791</v>
+        <v>76764</v>
       </c>
       <c r="D50" t="n">
-        <v>-1486.81</v>
+        <v>-746.39</v>
       </c>
       <c r="E50" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F50" t="n">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="G50" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1544</v>
+      </c>
+      <c r="L50" t="n">
+        <v>105</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:37.367</t>
+          <t>2026-05-29 09:47:59.073</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779509312953</v>
+        <v>1780022877746</v>
       </c>
       <c r="C51" t="n">
-        <v>88370</v>
+        <v>76782</v>
       </c>
       <c r="D51" t="n">
-        <v>166.53</v>
+        <v>-691.0700000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F51" t="n">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="G51" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1326</v>
+      </c>
+      <c r="L51" t="n">
+        <v>109</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.846</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:37.374</t>
+          <t>2026-05-29 09:48:00.875</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779509313154</v>
+        <v>1780022877946</v>
       </c>
       <c r="C52" t="n">
-        <v>88388</v>
+        <v>76849</v>
       </c>
       <c r="D52" t="n">
-        <v>176.2</v>
+        <v>-589.52</v>
       </c>
       <c r="E52" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F52" t="n">
-        <v>3644</v>
+        <v>619</v>
       </c>
       <c r="G52" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2928</v>
+      </c>
+      <c r="L52" t="n">
+        <v>111</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.508</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:37.625</t>
+          <t>2026-05-29 09:48:00.877</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779509313355</v>
+        <v>1780022878146</v>
       </c>
       <c r="C53" t="n">
-        <v>88745</v>
+        <v>76907</v>
       </c>
       <c r="D53" t="n">
-        <v>524.39</v>
+        <v>-502.04</v>
       </c>
       <c r="E53" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F53" t="n">
-        <v>3644</v>
+        <v>619</v>
       </c>
       <c r="G53" t="n">
-        <v>279.88</v>
+        <v>328.7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2730</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.114</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:37.627</t>
+          <t>2026-05-29 09:48:00.878</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779509313557</v>
+        <v>1780022878346</v>
       </c>
       <c r="C54" t="n">
-        <v>89043</v>
+        <v>76668</v>
       </c>
       <c r="D54" t="n">
-        <v>796.17</v>
+        <v>-715.9400000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F54" t="n">
-        <v>3644</v>
+        <v>1499</v>
       </c>
       <c r="G54" t="n">
-        <v>279.88</v>
+        <v>359.81</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2531</v>
+      </c>
+      <c r="L54" t="n">
+        <v>112</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.019</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:37.913</t>
+          <t>2026-05-29 09:48:00.880</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779509313758</v>
+        <v>1780022878546</v>
       </c>
       <c r="C55" t="n">
-        <v>88763</v>
+        <v>76741</v>
       </c>
       <c r="D55" t="n">
-        <v>476.36</v>
+        <v>-607.14</v>
       </c>
       <c r="E55" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F55" t="n">
-        <v>3644</v>
+        <v>1499</v>
       </c>
       <c r="G55" t="n">
-        <v>279.88</v>
+        <v>359.81</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2333</v>
+      </c>
+      <c r="L55" t="n">
+        <v>110</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.316</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:38.183</t>
+          <t>2026-05-29 09:48:00.918</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779509313960</v>
+        <v>1780022878746</v>
       </c>
       <c r="C56" t="n">
-        <v>88299</v>
+        <v>76862</v>
       </c>
       <c r="D56" t="n">
-        <v>-11.45</v>
+        <v>-455.79</v>
       </c>
       <c r="E56" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F56" t="n">
-        <v>3644</v>
+        <v>1499</v>
       </c>
       <c r="G56" t="n">
-        <v>279.88</v>
+        <v>359.81</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2170</v>
+      </c>
+      <c r="L56" t="n">
+        <v>114</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2.053</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:38.467</t>
+          <t>2026-05-29 09:48:00.942</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779509314161</v>
+        <v>1780022878946</v>
       </c>
       <c r="C57" t="n">
-        <v>88003</v>
+        <v>76609</v>
       </c>
       <c r="D57" t="n">
-        <v>-306.88</v>
+        <v>-686</v>
       </c>
       <c r="E57" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F57" t="n">
-        <v>3644</v>
+        <v>620</v>
       </c>
       <c r="G57" t="n">
-        <v>279.88</v>
+        <v>361.91</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1995</v>
+      </c>
+      <c r="L57" t="n">
+        <v>104</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.712</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:38.468</t>
+          <t>2026-05-29 09:48:01.228</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779509314362</v>
+        <v>1780022879146</v>
       </c>
       <c r="C58" t="n">
-        <v>88327</v>
+        <v>76698</v>
       </c>
       <c r="D58" t="n">
-        <v>32.46</v>
+        <v>-562.7</v>
       </c>
       <c r="E58" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F58" t="n">
-        <v>3644</v>
+        <v>620</v>
       </c>
       <c r="G58" t="n">
-        <v>279.88</v>
+        <v>361.91</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>2080</v>
+      </c>
+      <c r="L58" t="n">
+        <v>108</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.337</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:38.768</t>
+          <t>2026-05-29 09:48:01.241</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779509314564</v>
+        <v>1780022879365</v>
       </c>
       <c r="C59" t="n">
-        <v>88243</v>
+        <v>76805</v>
       </c>
       <c r="D59" t="n">
-        <v>-53.16</v>
+        <v>-427.56</v>
       </c>
       <c r="E59" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F59" t="n">
-        <v>3644</v>
+        <v>620</v>
       </c>
       <c r="G59" t="n">
-        <v>279.88</v>
+        <v>361.91</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J59" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1874</v>
+      </c>
+      <c r="L59" t="n">
+        <v>107</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.358</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:39.024</t>
+          <t>2026-05-29 09:48:01.244</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779509314765</v>
+        <v>1780022879565</v>
       </c>
       <c r="C60" t="n">
-        <v>88115</v>
+        <v>76883</v>
       </c>
       <c r="D60" t="n">
-        <v>-178.5</v>
+        <v>-328.18</v>
       </c>
       <c r="E60" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F60" t="n">
-        <v>3644</v>
+        <v>639</v>
       </c>
       <c r="G60" t="n">
-        <v>279.88</v>
+        <v>358.94</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1677</v>
+      </c>
+      <c r="L60" t="n">
+        <v>107</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.666</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:39.373</t>
+          <t>2026-05-29 09:48:02.092</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779509314966</v>
+        <v>1780022879765</v>
       </c>
       <c r="C61" t="n">
-        <v>88468</v>
+        <v>76721</v>
       </c>
       <c r="D61" t="n">
-        <v>183.42</v>
+        <v>-473.78</v>
       </c>
       <c r="E61" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F61" t="n">
-        <v>3644</v>
+        <v>639</v>
       </c>
       <c r="G61" t="n">
-        <v>279.88</v>
+        <v>358.94</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J61" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2326</v>
+      </c>
+      <c r="L61" t="n">
+        <v>106</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.106</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:39.621</t>
+          <t>2026-05-29 09:48:02.156</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779509315168</v>
+        <v>1780022880365</v>
       </c>
       <c r="C62" t="n">
-        <v>88805</v>
+        <v>76696</v>
       </c>
       <c r="D62" t="n">
-        <v>511.25</v>
+        <v>-475.09</v>
       </c>
       <c r="E62" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F62" t="n">
-        <v>3644</v>
+        <v>639</v>
       </c>
       <c r="G62" t="n">
-        <v>279.88</v>
+        <v>358.94</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1790</v>
+      </c>
+      <c r="L62" t="n">
+        <v>113</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.924</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:39.622</t>
+          <t>2026-05-29 09:48:02.157</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779509315369</v>
+        <v>1780022880565</v>
       </c>
       <c r="C63" t="n">
-        <v>88513</v>
+        <v>76765</v>
       </c>
       <c r="D63" t="n">
-        <v>193.69</v>
+        <v>-382.33</v>
       </c>
       <c r="E63" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F63" t="n">
-        <v>3644</v>
+        <v>639</v>
       </c>
       <c r="G63" t="n">
-        <v>279.88</v>
+        <v>358.94</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1591</v>
+      </c>
+      <c r="L63" t="n">
+        <v>108</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.893</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:39.884</t>
+          <t>2026-05-29 09:48:02.683</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779509315570</v>
+        <v>1780022880765</v>
       </c>
       <c r="C64" t="n">
-        <v>88590</v>
+        <v>76849</v>
       </c>
       <c r="D64" t="n">
-        <v>261</v>
+        <v>-279.22</v>
       </c>
       <c r="E64" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F64" t="n">
-        <v>3644</v>
+        <v>1280</v>
       </c>
       <c r="G64" t="n">
-        <v>279.88</v>
+        <v>375.13</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1916</v>
+      </c>
+      <c r="L64" t="n">
+        <v>111</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.229</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:39.906</t>
+          <t>2026-05-29 09:48:02.685</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779509315772</v>
+        <v>1780022880965</v>
       </c>
       <c r="C65" t="n">
-        <v>88756</v>
+        <v>76779</v>
       </c>
       <c r="D65" t="n">
-        <v>413.95</v>
+        <v>-335.25</v>
       </c>
       <c r="E65" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F65" t="n">
-        <v>3644</v>
+        <v>1280</v>
       </c>
       <c r="G65" t="n">
-        <v>279.88</v>
+        <v>375.13</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1718</v>
+      </c>
+      <c r="L65" t="n">
+        <v>118</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.322</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:40.194</t>
+          <t>2026-05-29 09:48:02.692</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779509315973</v>
+        <v>1780022881184</v>
       </c>
       <c r="C66" t="n">
-        <v>88362</v>
+        <v>76712</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.74</v>
+        <v>-385.49</v>
       </c>
       <c r="E66" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F66" t="n">
-        <v>3644</v>
+        <v>1280</v>
       </c>
       <c r="G66" t="n">
-        <v>279.88</v>
+        <v>375.13</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1506</v>
+      </c>
+      <c r="L66" t="n">
+        <v>114</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.106</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:40.446</t>
+          <t>2026-05-29 09:48:02.693</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779509316174</v>
+        <v>1780022881384</v>
       </c>
       <c r="C67" t="n">
-        <v>88439</v>
+        <v>76820</v>
       </c>
       <c r="D67" t="n">
-        <v>76.29000000000001</v>
+        <v>-258.22</v>
       </c>
       <c r="E67" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F67" t="n">
-        <v>3644</v>
+        <v>1280</v>
       </c>
       <c r="G67" t="n">
-        <v>279.88</v>
+        <v>375.13</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1308</v>
+      </c>
+      <c r="L67" t="n">
+        <v>113</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.232</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:41.012</t>
+          <t>2026-05-29 09:48:03.147</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779509316376</v>
+        <v>1780022881584</v>
       </c>
       <c r="C68" t="n">
-        <v>88622</v>
+        <v>76928</v>
       </c>
       <c r="D68" t="n">
-        <v>255.48</v>
+        <v>-137.31</v>
       </c>
       <c r="E68" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F68" t="n">
-        <v>3644</v>
+        <v>799</v>
       </c>
       <c r="G68" t="n">
-        <v>279.88</v>
+        <v>371.68</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1562</v>
+      </c>
+      <c r="L68" t="n">
+        <v>109</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.888</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:41.287</t>
+          <t>2026-05-29 09:48:03.149</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779509316577</v>
+        <v>1780022881784</v>
       </c>
       <c r="C69" t="n">
-        <v>88489</v>
+        <v>76680</v>
       </c>
       <c r="D69" t="n">
-        <v>109.71</v>
+        <v>-378.44</v>
       </c>
       <c r="E69" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F69" t="n">
-        <v>3403</v>
+        <v>799</v>
       </c>
       <c r="G69" t="n">
-        <v>279.88</v>
+        <v>371.68</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L69" t="n">
+        <v>116</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.354</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:41.304</t>
+          <t>2026-05-29 09:48:03.150</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779509316779</v>
+        <v>1780022881984</v>
       </c>
       <c r="C70" t="n">
-        <v>88393</v>
+        <v>76762</v>
       </c>
       <c r="D70" t="n">
-        <v>8.220000000000001</v>
+        <v>-277.52</v>
       </c>
       <c r="E70" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F70" t="n">
-        <v>3403</v>
+        <v>799</v>
       </c>
       <c r="G70" t="n">
-        <v>279.88</v>
+        <v>371.68</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L70" t="n">
+        <v>105</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:41.306</t>
+          <t>2026-05-29 09:48:03.151</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779509316980</v>
+        <v>1780022882184</v>
       </c>
       <c r="C71" t="n">
-        <v>88512</v>
+        <v>76881</v>
       </c>
       <c r="D71" t="n">
-        <v>126.81</v>
+        <v>-144.64</v>
       </c>
       <c r="E71" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F71" t="n">
-        <v>3403</v>
+        <v>799</v>
       </c>
       <c r="G71" t="n">
-        <v>279.88</v>
+        <v>371.68</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>966</v>
+      </c>
+      <c r="L71" t="n">
+        <v>106</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.624</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:41.554</t>
+          <t>2026-05-29 09:48:03.506</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779509317181</v>
+        <v>1780022882385</v>
       </c>
       <c r="C72" t="n">
-        <v>88586</v>
+        <v>76925</v>
       </c>
       <c r="D72" t="n">
-        <v>194.47</v>
+        <v>-93.41</v>
       </c>
       <c r="E72" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F72" t="n">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="G72" t="n">
-        <v>280.13</v>
+        <v>327.33</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L72" t="n">
+        <v>145</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.547</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:41.555</t>
+          <t>2026-05-29 09:48:03.519</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779509317383</v>
+        <v>1780022882604</v>
       </c>
       <c r="C73" t="n">
-        <v>88241</v>
+        <v>76825</v>
       </c>
       <c r="D73" t="n">
-        <v>-160.25</v>
+        <v>-188.74</v>
       </c>
       <c r="E73" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F73" t="n">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="G73" t="n">
-        <v>280.13</v>
+        <v>327.33</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K73" t="n">
+        <v>913</v>
+      </c>
+      <c r="L73" t="n">
+        <v>114</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.682</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.039</t>
+          <t>2026-05-29 09:48:04.218</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779509317584</v>
+        <v>1780022882804</v>
       </c>
       <c r="C74" t="n">
-        <v>88350</v>
+        <v>76941</v>
       </c>
       <c r="D74" t="n">
-        <v>-43.24</v>
+        <v>-63.3</v>
       </c>
       <c r="E74" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F74" t="n">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="G74" t="n">
-        <v>280.13</v>
+        <v>327.33</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1413</v>
+      </c>
+      <c r="L74" t="n">
+        <v>115</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.997</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.334</t>
+          <t>2026-05-29 09:48:04.307</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779509317785</v>
+        <v>1780022883023</v>
       </c>
       <c r="C75" t="n">
-        <v>88600</v>
+        <v>77045</v>
       </c>
       <c r="D75" t="n">
-        <v>208.92</v>
+        <v>43.86</v>
       </c>
       <c r="E75" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F75" t="n">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="G75" t="n">
-        <v>280.13</v>
+        <v>328.96</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1283</v>
+      </c>
+      <c r="L75" t="n">
+        <v>110</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.716</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.347</t>
+          <t>2026-05-29 09:48:05.565</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779509317987</v>
+        <v>1780022883223</v>
       </c>
       <c r="C76" t="n">
-        <v>88263</v>
+        <v>76956</v>
       </c>
       <c r="D76" t="n">
-        <v>-138.53</v>
+        <v>-47.33</v>
       </c>
       <c r="E76" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="G76" t="n">
-        <v>267.75</v>
+        <v>328.96</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2341</v>
+      </c>
+      <c r="L76" t="n">
+        <v>119</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.555</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.351</t>
+          <t>2026-05-29 09:48:05.606</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779509318188</v>
+        <v>1780022883423</v>
       </c>
       <c r="C77" t="n">
-        <v>88210</v>
+        <v>76924</v>
       </c>
       <c r="D77" t="n">
-        <v>-184.6</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F77" t="n">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="G77" t="n">
-        <v>267.75</v>
+        <v>328.96</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2182</v>
+      </c>
+      <c r="L77" t="n">
+        <v>115</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.819</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.557</t>
+          <t>2026-05-29 09:48:05.608</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779509318389</v>
+        <v>1780022883623</v>
       </c>
       <c r="C78" t="n">
-        <v>88304</v>
+        <v>77016</v>
       </c>
       <c r="D78" t="n">
-        <v>-81.37</v>
+        <v>18.88</v>
       </c>
       <c r="E78" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F78" t="n">
-        <v>685</v>
+        <v>640</v>
       </c>
       <c r="G78" t="n">
-        <v>267.75</v>
+        <v>328.96</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1984</v>
+      </c>
+      <c r="L78" t="n">
+        <v>107</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.868</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.560</t>
+          <t>2026-05-29 09:48:05.610</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779509318591</v>
+        <v>1780022883823</v>
       </c>
       <c r="C79" t="n">
-        <v>88464</v>
+        <v>76867</v>
       </c>
       <c r="D79" t="n">
-        <v>82.7</v>
+        <v>-131.06</v>
       </c>
       <c r="E79" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F79" t="n">
-        <v>765</v>
+        <v>839</v>
       </c>
       <c r="G79" t="n">
-        <v>267.06</v>
+        <v>328.55</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1785</v>
+      </c>
+      <c r="L79" t="n">
+        <v>115</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.494</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:42.829</t>
+          <t>2026-05-29 09:48:05.612</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779509318792</v>
+        <v>1780022884023</v>
       </c>
       <c r="C80" t="n">
-        <v>88119</v>
+        <v>76860</v>
       </c>
       <c r="D80" t="n">
-        <v>-266.44</v>
+        <v>-131.51</v>
       </c>
       <c r="E80" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F80" t="n">
-        <v>765</v>
+        <v>839</v>
       </c>
       <c r="G80" t="n">
-        <v>267.06</v>
+        <v>328.55</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1588</v>
+      </c>
+      <c r="L80" t="n">
+        <v>111</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.949</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:43.105</t>
+          <t>2026-05-29 09:48:05.613</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779509318994</v>
+        <v>1780022884223</v>
       </c>
       <c r="C81" t="n">
-        <v>88258</v>
+        <v>76953</v>
       </c>
       <c r="D81" t="n">
-        <v>-114.11</v>
+        <v>-31.93</v>
       </c>
       <c r="E81" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>765</v>
+        <v>839</v>
       </c>
       <c r="G81" t="n">
-        <v>267.06</v>
+        <v>328.55</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1389</v>
+      </c>
+      <c r="L81" t="n">
+        <v>102</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.911</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:43.373</t>
+          <t>2026-05-29 09:48:05.615</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779509319195</v>
+        <v>1780022884423</v>
       </c>
       <c r="C82" t="n">
-        <v>88369</v>
+        <v>77052</v>
       </c>
       <c r="D82" t="n">
-        <v>2.59</v>
+        <v>68.66</v>
       </c>
       <c r="E82" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F82" t="n">
-        <v>765</v>
+        <v>660</v>
       </c>
       <c r="G82" t="n">
-        <v>267.06</v>
+        <v>307.91</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1191</v>
+      </c>
+      <c r="L82" t="n">
+        <v>104</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.182</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:43.392</t>
+          <t>2026-05-29 09:48:06.163</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779509319396</v>
+        <v>1780022884623</v>
       </c>
       <c r="C83" t="n">
-        <v>88038</v>
+        <v>76780</v>
       </c>
       <c r="D83" t="n">
-        <v>-328.54</v>
+        <v>-206.77</v>
       </c>
       <c r="E83" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F83" t="n">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="G83" t="n">
-        <v>269.15</v>
+        <v>307.91</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1539</v>
+      </c>
+      <c r="L83" t="n">
+        <v>109</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.523</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:43.880</t>
+          <t>2026-05-29 09:48:06.165</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779509319598</v>
+        <v>1780022884842</v>
       </c>
       <c r="C84" t="n">
-        <v>88107</v>
+        <v>76862</v>
       </c>
       <c r="D84" t="n">
-        <v>-243.11</v>
+        <v>-114.43</v>
       </c>
       <c r="E84" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F84" t="n">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="G84" t="n">
-        <v>269.15</v>
+        <v>307.91</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J84" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1322</v>
+      </c>
+      <c r="L84" t="n">
+        <v>113</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.794</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:44.157</t>
+          <t>2026-05-29 09:48:06.166</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779509319799</v>
+        <v>1780022885042</v>
       </c>
       <c r="C85" t="n">
-        <v>88186</v>
+        <v>76989</v>
       </c>
       <c r="D85" t="n">
-        <v>-151.96</v>
+        <v>18.29</v>
       </c>
       <c r="E85" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F85" t="n">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="G85" t="n">
-        <v>269.15</v>
+        <v>307.91</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L85" t="n">
+        <v>111</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:44.159</t>
+          <t>2026-05-29 09:48:06.175</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779509320000</v>
+        <v>1780022885242</v>
       </c>
       <c r="C86" t="n">
-        <v>88330</v>
+        <v>76840</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.36</v>
+        <v>-131.62</v>
       </c>
       <c r="E86" t="n">
         <v>84</v>
       </c>
       <c r="F86" t="n">
-        <v>765</v>
+        <v>699</v>
       </c>
       <c r="G86" t="n">
-        <v>83.72</v>
+        <v>302.77</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K86" t="n">
+        <v>932</v>
+      </c>
+      <c r="L86" t="n">
+        <v>96</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:44.478</t>
+          <t>2026-05-29 09:48:07.084</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779509320202</v>
+        <v>1780022885442</v>
       </c>
       <c r="C87" t="n">
-        <v>87944</v>
+        <v>76890</v>
       </c>
       <c r="D87" t="n">
-        <v>-386.34</v>
+        <v>-75.04000000000001</v>
       </c>
       <c r="E87" t="n">
         <v>84</v>
       </c>
       <c r="F87" t="n">
-        <v>765</v>
+        <v>699</v>
       </c>
       <c r="G87" t="n">
-        <v>83.72</v>
+        <v>302.77</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1640</v>
+      </c>
+      <c r="L87" t="n">
+        <v>111</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:44.746</t>
+          <t>2026-05-29 09:48:07.114</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779509320403</v>
+        <v>1780022885642</v>
       </c>
       <c r="C88" t="n">
-        <v>88059</v>
+        <v>77069</v>
       </c>
       <c r="D88" t="n">
-        <v>-252.02</v>
+        <v>107.71</v>
       </c>
       <c r="E88" t="n">
         <v>84</v>
       </c>
       <c r="F88" t="n">
-        <v>765</v>
+        <v>699</v>
       </c>
       <c r="G88" t="n">
-        <v>83.72</v>
+        <v>302.77</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1471</v>
+      </c>
+      <c r="L88" t="n">
+        <v>103</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.985</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:44.767</t>
+          <t>2026-05-29 09:48:07.389</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779509320605</v>
+        <v>1780022885842</v>
       </c>
       <c r="C89" t="n">
-        <v>88450</v>
+        <v>76986</v>
       </c>
       <c r="D89" t="n">
-        <v>151.58</v>
+        <v>19.32</v>
       </c>
       <c r="E89" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F89" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="G89" t="n">
-        <v>71.76000000000001</v>
+        <v>200.28</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1545</v>
+      </c>
+      <c r="L89" t="n">
+        <v>106</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.384</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:45.100</t>
+          <t>2026-05-29 09:48:07.668</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779509320806</v>
+        <v>1780022886042</v>
       </c>
       <c r="C90" t="n">
-        <v>87864</v>
+        <v>76696</v>
       </c>
       <c r="D90" t="n">
-        <v>-442</v>
+        <v>-271.64</v>
       </c>
       <c r="E90" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F90" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="G90" t="n">
-        <v>71.76000000000001</v>
+        <v>200.28</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1625</v>
+      </c>
+      <c r="L90" t="n">
+        <v>108</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:45.384</t>
+          <t>2026-05-29 09:48:07.669</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779509321007</v>
+        <v>1780022886242</v>
       </c>
       <c r="C91" t="n">
-        <v>87923</v>
+        <v>76802</v>
       </c>
       <c r="D91" t="n">
-        <v>-360.9</v>
+        <v>-152.06</v>
       </c>
       <c r="E91" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F91" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="G91" t="n">
-        <v>71.76000000000001</v>
+        <v>200.28</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1426</v>
+      </c>
+      <c r="L91" t="n">
+        <v>105</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.917</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:45.385</t>
+          <t>2026-05-29 09:48:07.670</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779509321209</v>
+        <v>1780022886461</v>
       </c>
       <c r="C92" t="n">
-        <v>88126</v>
+        <v>76916</v>
       </c>
       <c r="D92" t="n">
-        <v>-139.86</v>
+        <v>-30.46</v>
       </c>
       <c r="E92" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F92" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="G92" t="n">
-        <v>71.76000000000001</v>
+        <v>200.28</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L92" t="n">
+        <v>109</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:45.661</t>
+          <t>2026-05-29 09:48:08.071</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779509321410</v>
+        <v>1780022886661</v>
       </c>
       <c r="C93" t="n">
-        <v>87850</v>
+        <v>76604</v>
       </c>
       <c r="D93" t="n">
-        <v>-408.86</v>
+        <v>-340.93</v>
       </c>
       <c r="E93" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F93" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G93" t="n">
-        <v>70.63</v>
+        <v>198.11</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1409</v>
+      </c>
+      <c r="L93" t="n">
+        <v>103</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:45.668</t>
+          <t>2026-05-29 09:48:08.072</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779509321611</v>
+        <v>1780022886861</v>
       </c>
       <c r="C94" t="n">
-        <v>87938</v>
+        <v>76670</v>
       </c>
       <c r="D94" t="n">
-        <v>-300.42</v>
+        <v>-257.89</v>
       </c>
       <c r="E94" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F94" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G94" t="n">
-        <v>70.63</v>
+        <v>198.11</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1210</v>
+      </c>
+      <c r="L94" t="n">
+        <v>109</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.918</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:46.049</t>
+          <t>2026-05-29 09:48:08.073</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779509321813</v>
+        <v>1780022887061</v>
       </c>
       <c r="C95" t="n">
-        <v>88067</v>
+        <v>76739</v>
       </c>
       <c r="D95" t="n">
-        <v>-156.4</v>
+        <v>-175.99</v>
       </c>
       <c r="E95" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F95" t="n">
-        <v>745</v>
+        <v>879</v>
       </c>
       <c r="G95" t="n">
-        <v>70.63</v>
+        <v>198.11</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1011</v>
+      </c>
+      <c r="L95" t="n">
+        <v>109</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.036</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:46.337</t>
+          <t>2026-05-29 09:48:08.306</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779509322014</v>
+        <v>1780022887261</v>
       </c>
       <c r="C96" t="n">
-        <v>88127</v>
+        <v>76795</v>
       </c>
       <c r="D96" t="n">
-        <v>-88.58</v>
+        <v>-111.19</v>
       </c>
       <c r="E96" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F96" t="n">
-        <v>524</v>
+        <v>680</v>
       </c>
       <c r="G96" t="n">
-        <v>78.98999999999999</v>
+        <v>195.33</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L96" t="n">
+        <v>107</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:46.584</t>
+          <t>2026-05-29 09:48:08.308</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779509322215</v>
+        <v>1780022887461</v>
       </c>
       <c r="C97" t="n">
-        <v>87959</v>
+        <v>76602</v>
       </c>
       <c r="D97" t="n">
-        <v>-252.15</v>
+        <v>-298.63</v>
       </c>
       <c r="E97" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F97" t="n">
-        <v>524</v>
+        <v>680</v>
       </c>
       <c r="G97" t="n">
-        <v>78.98999999999999</v>
+        <v>195.33</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>846</v>
+      </c>
+      <c r="L97" t="n">
+        <v>105</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.825</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:46.598</t>
+          <t>2026-05-29 09:48:08.782</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779509322417</v>
+        <v>1780022887661</v>
       </c>
       <c r="C98" t="n">
-        <v>88198</v>
+        <v>76736</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.54</v>
+        <v>-149.7</v>
       </c>
       <c r="E98" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F98" t="n">
-        <v>524</v>
+        <v>680</v>
       </c>
       <c r="G98" t="n">
-        <v>78.98999999999999</v>
+        <v>195.33</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L98" t="n">
+        <v>106</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.348</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:46.974</t>
+          <t>2026-05-29 09:48:08.795</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779509322618</v>
+        <v>1780022887861</v>
       </c>
       <c r="C99" t="n">
-        <v>88279</v>
+        <v>76953</v>
       </c>
       <c r="D99" t="n">
-        <v>80.48</v>
+        <v>74.78</v>
       </c>
       <c r="E99" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F99" t="n">
-        <v>644</v>
+        <v>560</v>
       </c>
       <c r="G99" t="n">
-        <v>79.91</v>
+        <v>101.24</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>933</v>
+      </c>
+      <c r="L99" t="n">
+        <v>105</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.722</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:47.273</t>
+          <t>2026-05-29 09:48:09.203</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779509322819</v>
+        <v>1780022888061</v>
       </c>
       <c r="C100" t="n">
-        <v>87772</v>
+        <v>76767</v>
       </c>
       <c r="D100" t="n">
-        <v>-430.54</v>
+        <v>-114.96</v>
       </c>
       <c r="E100" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F100" t="n">
-        <v>644</v>
+        <v>560</v>
       </c>
       <c r="G100" t="n">
-        <v>79.91</v>
+        <v>101.24</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1141</v>
+      </c>
+      <c r="L100" t="n">
+        <v>109</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.503</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:47.274</t>
+          <t>2026-05-29 09:48:09.249</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779509323021</v>
+        <v>1780022888280</v>
       </c>
       <c r="C101" t="n">
-        <v>87947</v>
+        <v>77160</v>
       </c>
       <c r="D101" t="n">
-        <v>-234.01</v>
+        <v>283.79</v>
       </c>
       <c r="E101" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F101" t="n">
-        <v>644</v>
+        <v>560</v>
       </c>
       <c r="G101" t="n">
-        <v>79.91</v>
+        <v>101.24</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>968</v>
+      </c>
+      <c r="L101" t="n">
+        <v>107</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.145</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:47.550</t>
+          <t>2026-05-29 09:48:09.506</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779509323222</v>
+        <v>1780022888480</v>
       </c>
       <c r="C102" t="n">
-        <v>88108</v>
+        <v>77025</v>
       </c>
       <c r="D102" t="n">
-        <v>-61.31</v>
+        <v>134.6</v>
       </c>
       <c r="E102" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F102" t="n">
-        <v>644</v>
+        <v>560</v>
       </c>
       <c r="G102" t="n">
-        <v>79.91</v>
+        <v>101.24</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1025</v>
+      </c>
+      <c r="L102" t="n">
+        <v>106</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.924</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:47.551</t>
+          <t>2026-05-29 09:48:09.508</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779509323423</v>
+        <v>1780022888680</v>
       </c>
       <c r="C103" t="n">
-        <v>87781</v>
+        <v>76668</v>
       </c>
       <c r="D103" t="n">
-        <v>-385.25</v>
+        <v>-229.13</v>
       </c>
       <c r="E103" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F103" t="n">
-        <v>765</v>
+        <v>560</v>
       </c>
       <c r="G103" t="n">
-        <v>81.98</v>
+        <v>101.24</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>827</v>
+      </c>
+      <c r="L103" t="n">
+        <v>107</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.025</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:48.116</t>
+          <t>2026-05-29 09:48:10.136</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779509323625</v>
+        <v>1780022888880</v>
       </c>
       <c r="C104" t="n">
-        <v>87830</v>
+        <v>76603</v>
       </c>
       <c r="D104" t="n">
-        <v>-316.98</v>
+        <v>-282.67</v>
       </c>
       <c r="E104" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F104" t="n">
-        <v>765</v>
+        <v>560</v>
       </c>
       <c r="G104" t="n">
-        <v>81.98</v>
+        <v>101.24</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1255</v>
+      </c>
+      <c r="L104" t="n">
+        <v>106</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.787</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.296</t>
+          <t>2026-05-29 09:48:10.178</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779509323826</v>
+        <v>1780022889080</v>
       </c>
       <c r="C105" t="n">
-        <v>87982</v>
+        <v>76622</v>
       </c>
       <c r="D105" t="n">
-        <v>-149.13</v>
+        <v>-249.54</v>
       </c>
       <c r="E105" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F105" t="n">
-        <v>765</v>
+        <v>560</v>
       </c>
       <c r="G105" t="n">
-        <v>81.98</v>
+        <v>101.24</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1097</v>
+      </c>
+      <c r="L105" t="n">
+        <v>107</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.124</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.333</t>
+          <t>2026-05-29 09:48:10.230</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779509324028</v>
+        <v>1780022889280</v>
       </c>
       <c r="C106" t="n">
-        <v>87997</v>
+        <v>76708</v>
       </c>
       <c r="D106" t="n">
-        <v>-126.68</v>
+        <v>-151.06</v>
       </c>
       <c r="E106" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F106" t="n">
-        <v>665</v>
+        <v>560</v>
       </c>
       <c r="G106" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K106" t="n">
+        <v>949</v>
+      </c>
+      <c r="L106" t="n">
+        <v>106</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.335</t>
+          <t>2026-05-29 09:48:10.231</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779509324230</v>
+        <v>1780022889480</v>
       </c>
       <c r="C107" t="n">
-        <v>87733</v>
+        <v>76497</v>
       </c>
       <c r="D107" t="n">
-        <v>-384.34</v>
+        <v>-354.51</v>
       </c>
       <c r="E107" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F107" t="n">
-        <v>665</v>
+        <v>560</v>
       </c>
       <c r="G107" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>750</v>
+      </c>
+      <c r="L107" t="n">
+        <v>104</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.843</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.344</t>
+          <t>2026-05-29 09:48:10.974</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779509324430</v>
+        <v>1780022889699</v>
       </c>
       <c r="C108" t="n">
-        <v>87891</v>
+        <v>77670</v>
       </c>
       <c r="D108" t="n">
-        <v>-207.13</v>
+        <v>836.22</v>
       </c>
       <c r="E108" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F108" t="n">
-        <v>665</v>
+        <v>560</v>
       </c>
       <c r="G108" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1274</v>
+      </c>
+      <c r="L108" t="n">
+        <v>106</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.122</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.386</t>
+          <t>2026-05-29 09:48:10.975</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779509324632</v>
+        <v>1780022889899</v>
       </c>
       <c r="C109" t="n">
-        <v>87941</v>
+        <v>78585</v>
       </c>
       <c r="D109" t="n">
-        <v>-146.77</v>
+        <v>1709.41</v>
       </c>
       <c r="E109" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F109" t="n">
-        <v>685</v>
+        <v>1918</v>
       </c>
       <c r="G109" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L109" t="n">
+        <v>116</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.394</t>
+          <t>2026-05-29 09:48:11.350</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779509324833</v>
+        <v>1780022890099</v>
       </c>
       <c r="C110" t="n">
-        <v>87585</v>
+        <v>83886</v>
       </c>
       <c r="D110" t="n">
-        <v>-495.43</v>
+        <v>6924.94</v>
       </c>
       <c r="E110" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F110" t="n">
-        <v>685</v>
+        <v>1918</v>
       </c>
       <c r="G110" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L110" t="n">
+        <v>110</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.318</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.587</t>
+          <t>2026-05-29 09:48:11.352</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779509325034</v>
+        <v>1780022890299</v>
       </c>
       <c r="C111" t="n">
-        <v>87655</v>
+        <v>86607</v>
       </c>
       <c r="D111" t="n">
-        <v>-400.66</v>
+        <v>9299.690000000001</v>
       </c>
       <c r="E111" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F111" t="n">
-        <v>685</v>
+        <v>1918</v>
       </c>
       <c r="G111" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1052</v>
+      </c>
+      <c r="L111" t="n">
+        <v>108</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.007</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.588</t>
+          <t>2026-05-29 09:48:11.487</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779509325236</v>
+        <v>1780022890499</v>
       </c>
       <c r="C112" t="n">
-        <v>87794</v>
+        <v>80904</v>
       </c>
       <c r="D112" t="n">
-        <v>-241.63</v>
+        <v>3131.7</v>
       </c>
       <c r="E112" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F112" t="n">
-        <v>685</v>
+        <v>1918</v>
       </c>
       <c r="G112" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K112" t="n">
+        <v>987</v>
+      </c>
+      <c r="L112" t="n">
+        <v>112</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.475</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.934</t>
+          <t>2026-05-29 09:48:11.526</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779509325437</v>
+        <v>1780022890699</v>
       </c>
       <c r="C113" t="n">
-        <v>87813</v>
+        <v>81337</v>
       </c>
       <c r="D113" t="n">
-        <v>-210.55</v>
+        <v>3408.12</v>
       </c>
       <c r="E113" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F113" t="n">
-        <v>765</v>
+        <v>1918</v>
       </c>
       <c r="G113" t="n">
-        <v>82.11</v>
+        <v>101.24</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>826</v>
+      </c>
+      <c r="L113" t="n">
+        <v>112</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.631</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-23 11:08:49.980</t>
+          <t>2026-05-29 09:49:10.077</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779509325638</v>
+        <v>1780022948983</v>
       </c>
       <c r="C114" t="n">
-        <v>87615</v>
+        <v>75093</v>
       </c>
       <c r="D114" t="n">
-        <v>-398.02</v>
+        <v>-3006.29</v>
       </c>
       <c r="E114" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F114" t="n">
-        <v>765</v>
+        <v>1099</v>
       </c>
       <c r="G114" t="n">
-        <v>82.11</v>
+        <v>291.49</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:50.187</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1779509325840</v>
-      </c>
-      <c r="C115" t="n">
-        <v>87767</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-226.12</v>
-      </c>
-      <c r="E115" t="n">
-        <v>83</v>
-      </c>
-      <c r="F115" t="n">
-        <v>765</v>
-      </c>
-      <c r="G115" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:50.189</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>1779509326041</v>
-      </c>
-      <c r="C116" t="n">
-        <v>88034</v>
-      </c>
-      <c r="D116" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="E116" t="n">
-        <v>87</v>
-      </c>
-      <c r="F116" t="n">
-        <v>624</v>
-      </c>
-      <c r="G116" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:50.546</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1779509326242</v>
-      </c>
-      <c r="C117" t="n">
-        <v>87528</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-456.42</v>
-      </c>
-      <c r="E117" t="n">
-        <v>87</v>
-      </c>
-      <c r="F117" t="n">
-        <v>624</v>
-      </c>
-      <c r="G117" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:50.902</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1779509326444</v>
-      </c>
-      <c r="C118" t="n">
-        <v>87641</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-320.6</v>
-      </c>
-      <c r="E118" t="n">
-        <v>87</v>
-      </c>
-      <c r="F118" t="n">
-        <v>624</v>
-      </c>
-      <c r="G118" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:50.904</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>1779509326645</v>
-      </c>
-      <c r="C119" t="n">
-        <v>87741</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-204.57</v>
-      </c>
-      <c r="E119" t="n">
-        <v>87</v>
-      </c>
-      <c r="F119" t="n">
-        <v>624</v>
-      </c>
-      <c r="G119" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:51.159</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1779509326847</v>
-      </c>
-      <c r="C120" t="n">
-        <v>87606</v>
-      </c>
-      <c r="D120" t="n">
-        <v>-329.34</v>
-      </c>
-      <c r="E120" t="n">
-        <v>83</v>
-      </c>
-      <c r="F120" t="n">
-        <v>805</v>
-      </c>
-      <c r="G120" t="n">
-        <v>87.58</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:51.505</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>1779509327048</v>
-      </c>
-      <c r="C121" t="n">
-        <v>87556</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-362.87</v>
-      </c>
-      <c r="E121" t="n">
-        <v>83</v>
-      </c>
-      <c r="F121" t="n">
-        <v>805</v>
-      </c>
-      <c r="G121" t="n">
-        <v>87.58</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:51.507</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1779509327249</v>
-      </c>
-      <c r="C122" t="n">
-        <v>87742</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-158.73</v>
-      </c>
-      <c r="E122" t="n">
-        <v>83</v>
-      </c>
-      <c r="F122" t="n">
-        <v>805</v>
-      </c>
-      <c r="G122" t="n">
-        <v>87.58</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:51.509</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1779509327451</v>
-      </c>
-      <c r="C123" t="n">
-        <v>87786</v>
-      </c>
-      <c r="D123" t="n">
-        <v>-106.79</v>
-      </c>
-      <c r="E123" t="n">
-        <v>87</v>
-      </c>
-      <c r="F123" t="n">
-        <v>584</v>
-      </c>
-      <c r="G123" t="n">
-        <v>89.77</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:51.742</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>1779509327652</v>
-      </c>
-      <c r="C124" t="n">
-        <v>87522</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-365.45</v>
-      </c>
-      <c r="E124" t="n">
-        <v>87</v>
-      </c>
-      <c r="F124" t="n">
-        <v>584</v>
-      </c>
-      <c r="G124" t="n">
-        <v>89.77</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:52.138</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1779509327853</v>
-      </c>
-      <c r="C125" t="n">
-        <v>87562</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-307.18</v>
-      </c>
-      <c r="E125" t="n">
-        <v>87</v>
-      </c>
-      <c r="F125" t="n">
-        <v>584</v>
-      </c>
-      <c r="G125" t="n">
-        <v>89.77</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:52.156</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>1779509328055</v>
-      </c>
-      <c r="C126" t="n">
-        <v>87859</v>
-      </c>
-      <c r="D126" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="E126" t="n">
-        <v>87</v>
-      </c>
-      <c r="F126" t="n">
-        <v>584</v>
-      </c>
-      <c r="G126" t="n">
-        <v>89.77</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:52.588</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>1779509328256</v>
-      </c>
-      <c r="C127" t="n">
-        <v>87461</v>
-      </c>
-      <c r="D127" t="n">
-        <v>-393.08</v>
-      </c>
-      <c r="E127" t="n">
-        <v>89</v>
-      </c>
-      <c r="F127" t="n">
-        <v>705</v>
-      </c>
-      <c r="G127" t="n">
-        <v>87.44</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:52.930</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>1779509328457</v>
-      </c>
-      <c r="C128" t="n">
-        <v>87689</v>
-      </c>
-      <c r="D128" t="n">
-        <v>-145.43</v>
-      </c>
-      <c r="E128" t="n">
-        <v>89</v>
-      </c>
-      <c r="F128" t="n">
-        <v>705</v>
-      </c>
-      <c r="G128" t="n">
-        <v>87.44</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:52.932</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>1779509328659</v>
-      </c>
-      <c r="C129" t="n">
-        <v>87978</v>
-      </c>
-      <c r="D129" t="n">
-        <v>150.84</v>
-      </c>
-      <c r="E129" t="n">
-        <v>95</v>
-      </c>
-      <c r="F129" t="n">
-        <v>503</v>
-      </c>
-      <c r="G129" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:53.231</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>1779509328860</v>
-      </c>
-      <c r="C130" t="n">
-        <v>87745</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-89.7</v>
-      </c>
-      <c r="E130" t="n">
-        <v>95</v>
-      </c>
-      <c r="F130" t="n">
-        <v>503</v>
-      </c>
-      <c r="G130" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:53.644</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>1779509329062</v>
-      </c>
-      <c r="C131" t="n">
-        <v>87558</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-272.21</v>
-      </c>
-      <c r="E131" t="n">
-        <v>95</v>
-      </c>
-      <c r="F131" t="n">
-        <v>503</v>
-      </c>
-      <c r="G131" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:53.988</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1779509329263</v>
-      </c>
-      <c r="C132" t="n">
-        <v>87503</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-313.6</v>
-      </c>
-      <c r="E132" t="n">
-        <v>95</v>
-      </c>
-      <c r="F132" t="n">
-        <v>503</v>
-      </c>
-      <c r="G132" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:53.993</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1779509329464</v>
-      </c>
-      <c r="C133" t="n">
-        <v>87779</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-21.92</v>
-      </c>
-      <c r="E133" t="n">
-        <v>95</v>
-      </c>
-      <c r="F133" t="n">
-        <v>503</v>
-      </c>
-      <c r="G133" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:54.000</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1779509329666</v>
-      </c>
-      <c r="C134" t="n">
-        <v>87243</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-556.83</v>
-      </c>
-      <c r="E134" t="n">
-        <v>92</v>
-      </c>
-      <c r="F134" t="n">
-        <v>967</v>
-      </c>
-      <c r="G134" t="n">
-        <v>129.02</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:54.256</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1779509329867</v>
-      </c>
-      <c r="C135" t="n">
-        <v>87359</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-412.99</v>
-      </c>
-      <c r="E135" t="n">
-        <v>92</v>
-      </c>
-      <c r="F135" t="n">
-        <v>967</v>
-      </c>
-      <c r="G135" t="n">
-        <v>129.02</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:54.257</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>1779509330068</v>
-      </c>
-      <c r="C136" t="n">
-        <v>87509</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-242.34</v>
-      </c>
-      <c r="E136" t="n">
-        <v>92</v>
-      </c>
-      <c r="F136" t="n">
-        <v>967</v>
-      </c>
-      <c r="G136" t="n">
-        <v>129.02</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:54.356</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1779509330270</v>
-      </c>
-      <c r="C137" t="n">
-        <v>87595</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-144.22</v>
-      </c>
-      <c r="E137" t="n">
-        <v>89</v>
-      </c>
-      <c r="F137" t="n">
-        <v>644</v>
-      </c>
-      <c r="G137" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:54.606</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>1779509330471</v>
-      </c>
-      <c r="C138" t="n">
-        <v>87098</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-634.01</v>
-      </c>
-      <c r="E138" t="n">
-        <v>89</v>
-      </c>
-      <c r="F138" t="n">
-        <v>644</v>
-      </c>
-      <c r="G138" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:54.891</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1779509330672</v>
-      </c>
-      <c r="C139" t="n">
-        <v>87389</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-311.31</v>
-      </c>
-      <c r="E139" t="n">
-        <v>89</v>
-      </c>
-      <c r="F139" t="n">
-        <v>644</v>
-      </c>
-      <c r="G139" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:55.185</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1779509330874</v>
-      </c>
-      <c r="C140" t="n">
-        <v>87460</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-224.74</v>
-      </c>
-      <c r="E140" t="n">
-        <v>91</v>
-      </c>
-      <c r="F140" t="n">
-        <v>665</v>
-      </c>
-      <c r="G140" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:55.186</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1779509331075</v>
-      </c>
-      <c r="C141" t="n">
-        <v>87504</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-169.51</v>
-      </c>
-      <c r="E141" t="n">
-        <v>91</v>
-      </c>
-      <c r="F141" t="n">
-        <v>665</v>
-      </c>
-      <c r="G141" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:55.440</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779509331276</v>
-      </c>
-      <c r="C142" t="n">
-        <v>87201</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-464.03</v>
-      </c>
-      <c r="E142" t="n">
-        <v>91</v>
-      </c>
-      <c r="F142" t="n">
-        <v>665</v>
-      </c>
-      <c r="G142" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:55.441</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779509331478</v>
-      </c>
-      <c r="C143" t="n">
-        <v>87373</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-268.83</v>
-      </c>
-      <c r="E143" t="n">
-        <v>91</v>
-      </c>
-      <c r="F143" t="n">
-        <v>665</v>
-      </c>
-      <c r="G143" t="n">
-        <v>128.63</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:55.760</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779509331679</v>
-      </c>
-      <c r="C144" t="n">
-        <v>87560</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-68.39</v>
-      </c>
-      <c r="E144" t="n">
-        <v>80</v>
-      </c>
-      <c r="F144" t="n">
-        <v>765</v>
-      </c>
-      <c r="G144" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:56.056</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779509331881</v>
-      </c>
-      <c r="C145" t="n">
-        <v>87311</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-313.97</v>
-      </c>
-      <c r="E145" t="n">
-        <v>80</v>
-      </c>
-      <c r="F145" t="n">
-        <v>765</v>
-      </c>
-      <c r="G145" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:56.340</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779509332082</v>
-      </c>
-      <c r="C146" t="n">
-        <v>87338</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-271.27</v>
-      </c>
-      <c r="E146" t="n">
-        <v>80</v>
-      </c>
-      <c r="F146" t="n">
-        <v>765</v>
-      </c>
-      <c r="G146" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:56.342</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779509332283</v>
-      </c>
-      <c r="C147" t="n">
-        <v>87659</v>
-      </c>
-      <c r="D147" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="E147" t="n">
-        <v>80</v>
-      </c>
-      <c r="F147" t="n">
-        <v>765</v>
-      </c>
-      <c r="G147" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:56.727</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779509332485</v>
-      </c>
-      <c r="C148" t="n">
-        <v>87878</v>
-      </c>
-      <c r="D148" t="n">
-        <v>279.13</v>
-      </c>
-      <c r="E148" t="n">
-        <v>87</v>
-      </c>
-      <c r="F148" t="n">
-        <v>684</v>
-      </c>
-      <c r="G148" t="n">
-        <v>128.64</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:56.999</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779509332686</v>
-      </c>
-      <c r="C149" t="n">
-        <v>87229</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-383.83</v>
-      </c>
-      <c r="E149" t="n">
-        <v>87</v>
-      </c>
-      <c r="F149" t="n">
-        <v>684</v>
-      </c>
-      <c r="G149" t="n">
-        <v>128.64</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:57.314</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779509332887</v>
-      </c>
-      <c r="C150" t="n">
-        <v>87255</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-338.64</v>
-      </c>
-      <c r="E150" t="n">
-        <v>87</v>
-      </c>
-      <c r="F150" t="n">
-        <v>684</v>
-      </c>
-      <c r="G150" t="n">
-        <v>128.64</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:57.316</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779509333089</v>
-      </c>
-      <c r="C151" t="n">
-        <v>87657</v>
-      </c>
-      <c r="D151" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="E151" t="n">
-        <v>87</v>
-      </c>
-      <c r="F151" t="n">
-        <v>684</v>
-      </c>
-      <c r="G151" t="n">
-        <v>128.64</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-23 11:08:57.579</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779509333290</v>
-      </c>
-      <c r="C152" t="n">
-        <v>87399</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-181.72</v>
-      </c>
-      <c r="E152" t="n">
-        <v>80</v>
-      </c>
-      <c r="F152" t="n">
-        <v>907</v>
-      </c>
-      <c r="G152" t="n">
-        <v>141.83</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I114" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L114" t="n">
+        <v>110</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.468</v>
       </c>
     </row>
   </sheetData>
